--- a/Results/MND_MIROCALS_vs_MND_RILUZOLE.xlsx
+++ b/Results/MND_MIROCALS_vs_MND_RILUZOLE.xlsx
@@ -441,12 +441,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>MND MIROCALS</t>
+          <t>MIROCALS MND</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>MND RILUZOLE</t>
+          <t>RILUZOLE MND</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
